--- a/datos/06-analisis-desviaciones -rendimientos.xlsx
+++ b/datos/06-analisis-desviaciones -rendimientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="983" documentId="8_{566A70F3-096B-4476-B336-90A9B7DB3344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93B4B361-36CE-40E1-B99F-139C20A30FF9}"/>
+  <xr:revisionPtr revIDLastSave="1009" documentId="8_{566A70F3-096B-4476-B336-90A9B7DB3344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0036DA0-24B5-45D8-86D0-D85536EC5F8F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="675" activeTab="3" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
   </bookViews>
@@ -718,7 +718,6 @@
     <definedName name="zzzzzzzzzzzzzzzzzz" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4261,6 +4260,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
